--- a/base03/polpa_metricas.xlsx
+++ b/base03/polpa_metricas.xlsx
@@ -464,7 +464,9 @@
       <c r="A2" t="n">
         <v>477.48</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>POLPA-202507-1999</t>
@@ -1131,7 +1133,9 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B30" t="n">
         <v>48.78</v>
       </c>
@@ -1188,7 +1192,9 @@
           <t>POLPA-202507-8699</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E32" t="n">
         <v>2.99</v>
       </c>
@@ -1898,7 +1904,9 @@
       <c r="A62" t="n">
         <v>348.51</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>POLPA-202507-7088</t>
@@ -2144,7 +2152,9 @@
           <t>POLPA-202507-9699</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E72" t="n">
         <v>2.18</v>
       </c>
@@ -2299,7 +2309,9 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B79" t="n">
         <v>0.51</v>
       </c>
@@ -2908,7 +2920,9 @@
           <t>POLPA-202507-4644</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E104" t="n">
         <v>2.95</v>
       </c>
@@ -3135,7 +3149,9 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B114" t="n">
         <v>81.70999999999999</v>
       </c>
@@ -3157,7 +3173,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B115" t="n">
         <v>21.76</v>
       </c>
@@ -3515,7 +3533,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B130" t="n">
         <v>79.91</v>
       </c>
@@ -3609,7 +3629,9 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B134" t="n">
         <v>282.3</v>
       </c>
@@ -3631,7 +3653,9 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B135" t="n">
         <v>3.22</v>
       </c>
@@ -4048,7 +4072,9 @@
           <t>POLPA-202507-8938</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E152" t="n">
         <v>1.92</v>
       </c>
@@ -4062,7 +4088,9 @@
       <c r="A153" t="n">
         <v>337.71</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
           <t>POLPA-202507-6205</t>
@@ -4548,7 +4576,9 @@
           <t>POLPA-202507-5375</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E173" t="n">
         <v>2.39</v>
       </c>
@@ -4570,7 +4600,9 @@
           <t>POLPA-202507-3418</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E174" t="n">
         <v>2.98</v>
       </c>
@@ -4904,7 +4936,9 @@
           <t>POLPA-202507-9183</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E188" t="n">
         <v>2.23</v>
       </c>
@@ -4974,7 +5008,9 @@
           <t>POLPA-202507-7112</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E191" t="n">
         <v>0.72</v>
       </c>
@@ -5596,7 +5632,9 @@
           <t>POLPA-202507-1123</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E217" t="n">
         <v>0.31</v>
       </c>
@@ -5778,7 +5816,9 @@
       <c r="A225" t="n">
         <v>441.67</v>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C225" t="inlineStr">
         <is>
           <t>POLPA-202507-6326</t>
@@ -6672,7 +6712,9 @@
           <t>POLPA-202507-6205</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E262" t="n">
         <v>3.2</v>
       </c>
@@ -6755,7 +6797,9 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B266" t="n">
         <v>167.61</v>
       </c>
@@ -7476,7 +7520,9 @@
       <c r="A296" t="n">
         <v>770.09</v>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C296" t="inlineStr">
         <is>
           <t>POLPA-202507-9559</t>
@@ -7930,7 +7976,9 @@
       <c r="A315" t="n">
         <v>107.16</v>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C315" t="inlineStr">
         <is>
           <t>POLPA-202507-9514</t>
@@ -8045,7 +8093,9 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B320" t="n">
         <v>24.05</v>
       </c>
@@ -8510,7 +8560,9 @@
           <t>POLPA-202507-1076</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E339" t="n">
         <v>2.72</v>
       </c>
@@ -8593,7 +8645,9 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr"/>
+      <c r="A343" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B343" t="n">
         <v>33.21</v>
       </c>
@@ -9842,7 +9896,9 @@
       <c r="A395" t="n">
         <v>621.1900000000001</v>
       </c>
-      <c r="B395" t="inlineStr"/>
+      <c r="B395" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C395" t="inlineStr">
         <is>
           <t>POLPA-202507-3910</t>
@@ -10056,7 +10112,9 @@
       <c r="A404" t="n">
         <v>237.7</v>
       </c>
-      <c r="B404" t="inlineStr"/>
+      <c r="B404" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C404" t="inlineStr">
         <is>
           <t>POLPA-202507-4318</t>
@@ -10894,7 +10952,9 @@
       <c r="A439" t="n">
         <v>274.65</v>
       </c>
-      <c r="B439" t="inlineStr"/>
+      <c r="B439" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C439" t="inlineStr">
         <is>
           <t>POLPA-202507-8652</t>
@@ -11105,7 +11165,9 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr"/>
+      <c r="A448" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B448" t="n">
         <v>276.41</v>
       </c>
@@ -11754,7 +11816,9 @@
       <c r="A475" t="n">
         <v>659.97</v>
       </c>
-      <c r="B475" t="inlineStr"/>
+      <c r="B475" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C475" t="inlineStr">
         <is>
           <t>POLPA-202507-8784</t>
@@ -11856,7 +11920,9 @@
           <t>POLPA-202507-1026</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E479" t="n">
         <v>1.56</v>
       </c>
@@ -12155,7 +12221,9 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr"/>
+      <c r="A492" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B492" t="n">
         <v>890.9400000000001</v>
       </c>
@@ -12548,7 +12616,9 @@
           <t>POLPA-202507-9896</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E508" t="n">
         <v>1.88</v>
       </c>
@@ -13650,7 +13720,9 @@
           <t>POLPA-202508-2661</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E554" t="n">
         <v>0.92</v>
       </c>
@@ -14768,7 +14840,9 @@
       <c r="A601" t="n">
         <v>1032.73</v>
       </c>
-      <c r="B601" t="inlineStr"/>
+      <c r="B601" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C601" t="inlineStr">
         <is>
           <t>POLPA-202508-5666</t>
@@ -14942,7 +15016,9 @@
           <t>POLPA-202508-7140</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E608" t="n">
         <v>0.88</v>
       </c>
@@ -15265,7 +15341,9 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr"/>
+      <c r="A622" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B622" t="n">
         <v>44.98</v>
       </c>
@@ -15938,7 +16016,9 @@
       <c r="A650" t="n">
         <v>291.13</v>
       </c>
-      <c r="B650" t="inlineStr"/>
+      <c r="B650" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C650" t="inlineStr">
         <is>
           <t>POLPA-202508-3229</t>
@@ -16941,7 +17021,9 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr"/>
+      <c r="A692" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B692" t="n">
         <v>24.33</v>
       </c>
@@ -17502,7 +17584,9 @@
           <t>POLPA-202508-8173</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E715" t="n">
         <v>0.88</v>
       </c>
@@ -18137,7 +18221,9 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr"/>
+      <c r="A742" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B742" t="n">
         <v>166.59</v>
       </c>
@@ -18458,7 +18544,9 @@
           <t>POLPA-202508-1601</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr"/>
+      <c r="D755" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E755" t="n">
         <v>0.9</v>
       </c>
@@ -18517,7 +18605,9 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr"/>
+      <c r="A758" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B758" t="n">
         <v>512.79</v>
       </c>
@@ -18718,7 +18808,9 @@
           <t>POLPA-202508-8575</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E766" t="n">
         <v>0.92</v>
       </c>
@@ -19188,7 +19280,9 @@
       <c r="A786" t="n">
         <v>726.17</v>
       </c>
-      <c r="B786" t="inlineStr"/>
+      <c r="B786" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C786" t="inlineStr">
         <is>
           <t>POLPA-202508-1382</t>
@@ -19210,7 +19304,9 @@
       <c r="A787" t="n">
         <v>1172.78</v>
       </c>
-      <c r="B787" t="inlineStr"/>
+      <c r="B787" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C787" t="inlineStr">
         <is>
           <t>POLPA-202508-3934</t>
@@ -19949,7 +20045,9 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr"/>
+      <c r="A818" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B818" t="n">
         <v>372.93</v>
       </c>
@@ -20390,7 +20488,9 @@
           <t>POLPA-202508-8714</t>
         </is>
       </c>
-      <c r="D836" t="inlineStr"/>
+      <c r="D836" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E836" t="n">
         <v>1.8</v>
       </c>
@@ -20572,7 +20672,9 @@
       <c r="A844" t="n">
         <v>567.29</v>
       </c>
-      <c r="B844" t="inlineStr"/>
+      <c r="B844" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C844" t="inlineStr">
         <is>
           <t>POLPA-202508-8312</t>
@@ -21191,7 +21293,9 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" t="inlineStr"/>
+      <c r="A870" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B870" t="n">
         <v>381.32</v>
       </c>
@@ -22064,7 +22168,9 @@
           <t>POLPA-202508-2591</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr"/>
+      <c r="D906" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E906" t="n">
         <v>0.51</v>
       </c>
@@ -22230,7 +22336,9 @@
           <t>POLPA-202508-4338</t>
         </is>
       </c>
-      <c r="D913" t="inlineStr"/>
+      <c r="D913" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E913" t="n">
         <v>2.76</v>
       </c>
@@ -22505,7 +22613,9 @@
       </c>
     </row>
     <row r="925">
-      <c r="A925" t="inlineStr"/>
+      <c r="A925" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B925" t="n">
         <v>297.56</v>
       </c>
@@ -22863,7 +22973,9 @@
       </c>
     </row>
     <row r="940">
-      <c r="A940" t="inlineStr"/>
+      <c r="A940" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B940" t="n">
         <v>182.41</v>
       </c>
@@ -22912,7 +23024,9 @@
       <c r="A942" t="n">
         <v>859.3</v>
       </c>
-      <c r="B942" t="inlineStr"/>
+      <c r="B942" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C942" t="inlineStr">
         <is>
           <t>POLPA-202508-9792</t>
@@ -23542,7 +23656,9 @@
           <t>POLPA-202508-2290</t>
         </is>
       </c>
-      <c r="D968" t="inlineStr"/>
+      <c r="D968" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E968" t="n">
         <v>1.28</v>
       </c>
@@ -23604,7 +23720,9 @@
       <c r="A971" t="n">
         <v>113.19</v>
       </c>
-      <c r="B971" t="inlineStr"/>
+      <c r="B971" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C971" t="inlineStr">
         <is>
           <t>POLPA-202508-6211</t>
@@ -23746,7 +23864,9 @@
       <c r="A977" t="n">
         <v>639.22</v>
       </c>
-      <c r="B977" t="inlineStr"/>
+      <c r="B977" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C977" t="inlineStr">
         <is>
           <t>POLPA-202508-2669</t>
@@ -23872,7 +23992,9 @@
           <t>POLPA-202508-5528</t>
         </is>
       </c>
-      <c r="D982" t="inlineStr"/>
+      <c r="D982" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E982" t="n">
         <v>2.31</v>
       </c>
@@ -23982,7 +24104,9 @@
       <c r="A987" t="n">
         <v>108.62</v>
       </c>
-      <c r="B987" t="inlineStr"/>
+      <c r="B987" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C987" t="inlineStr">
         <is>
           <t>POLPA-202508-5223</t>
@@ -24468,7 +24592,9 @@
           <t>POLPA-202508-3987</t>
         </is>
       </c>
-      <c r="D1007" t="inlineStr"/>
+      <c r="D1007" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1007" t="n">
         <v>2.47</v>
       </c>
@@ -24482,7 +24608,9 @@
       <c r="A1008" t="n">
         <v>673.95</v>
       </c>
-      <c r="B1008" t="inlineStr"/>
+      <c r="B1008" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1008" t="inlineStr">
         <is>
           <t>POLPA-202508-4991</t>
@@ -24717,7 +24845,9 @@
       </c>
     </row>
     <row r="1018">
-      <c r="A1018" t="inlineStr"/>
+      <c r="A1018" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1018" t="n">
         <v>922.45</v>
       </c>
@@ -25219,7 +25349,9 @@
       </c>
     </row>
     <row r="1039">
-      <c r="A1039" t="inlineStr"/>
+      <c r="A1039" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1039" t="n">
         <v>419.57</v>
       </c>
@@ -25433,7 +25565,9 @@
       </c>
     </row>
     <row r="1048">
-      <c r="A1048" t="inlineStr"/>
+      <c r="A1048" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1048" t="n">
         <v>78.16</v>
       </c>
@@ -26391,7 +26525,9 @@
       </c>
     </row>
     <row r="1088">
-      <c r="A1088" t="inlineStr"/>
+      <c r="A1088" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1088" t="n">
         <v>561.0700000000001</v>
       </c>
@@ -27120,7 +27256,9 @@
           <t>POLPA-202508-9276</t>
         </is>
       </c>
-      <c r="D1118" t="inlineStr"/>
+      <c r="D1118" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1118" t="n">
         <v>2.52</v>
       </c>
@@ -27238,7 +27376,9 @@
           <t>POLPA-202508-8443</t>
         </is>
       </c>
-      <c r="D1123" t="inlineStr"/>
+      <c r="D1123" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1123" t="n">
         <v>1.14</v>
       </c>
@@ -28572,7 +28712,9 @@
       <c r="A1179" t="n">
         <v>1014.18</v>
       </c>
-      <c r="B1179" t="inlineStr"/>
+      <c r="B1179" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1179" t="inlineStr">
         <is>
           <t>POLPA-202508-6156</t>
@@ -29263,7 +29405,9 @@
       </c>
     </row>
     <row r="1208">
-      <c r="A1208" t="inlineStr"/>
+      <c r="A1208" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1208" t="n">
         <v>558.72</v>
       </c>
@@ -30760,7 +30904,9 @@
           <t>POLPA-202509-5338</t>
         </is>
       </c>
-      <c r="D1270" t="inlineStr"/>
+      <c r="D1270" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1270" t="n">
         <v>1.49</v>
       </c>
@@ -31238,7 +31384,9 @@
           <t>POLPA-202509-9066</t>
         </is>
       </c>
-      <c r="D1290" t="inlineStr"/>
+      <c r="D1290" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1290" t="n">
         <v>2.79</v>
       </c>
@@ -31452,7 +31600,9 @@
           <t>POLPA-202509-7311</t>
         </is>
       </c>
-      <c r="D1299" t="inlineStr"/>
+      <c r="D1299" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1299" t="n">
         <v>1.32</v>
       </c>
@@ -32135,7 +32285,9 @@
       </c>
     </row>
     <row r="1328">
-      <c r="A1328" t="inlineStr"/>
+      <c r="A1328" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1328" t="n">
         <v>51.99</v>
       </c>
@@ -32544,7 +32696,9 @@
       <c r="A1345" t="n">
         <v>391.9</v>
       </c>
-      <c r="B1345" t="inlineStr"/>
+      <c r="B1345" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1345" t="inlineStr">
         <is>
           <t>POLPA-202509-5815</t>
@@ -33187,7 +33341,9 @@
       </c>
     </row>
     <row r="1372">
-      <c r="A1372" t="inlineStr"/>
+      <c r="A1372" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1372" t="n">
         <v>21.65</v>
       </c>
@@ -33580,7 +33736,9 @@
           <t>POLPA-202509-2951</t>
         </is>
       </c>
-      <c r="D1388" t="inlineStr"/>
+      <c r="D1388" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1388" t="n">
         <v>1.84</v>
       </c>
@@ -33615,7 +33773,9 @@
       </c>
     </row>
     <row r="1390">
-      <c r="A1390" t="inlineStr"/>
+      <c r="A1390" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1390" t="n">
         <v>203.23</v>
       </c>
@@ -33624,7 +33784,9 @@
           <t>POLPA-202509-4341</t>
         </is>
       </c>
-      <c r="D1390" t="inlineStr"/>
+      <c r="D1390" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1390" t="n">
         <v>1.36</v>
       </c>
@@ -33635,7 +33797,9 @@
       </c>
     </row>
     <row r="1391">
-      <c r="A1391" t="inlineStr"/>
+      <c r="A1391" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1391" t="n">
         <v>374.45</v>
       </c>
@@ -33924,7 +34088,9 @@
       <c r="A1403" t="n">
         <v>416.13</v>
       </c>
-      <c r="B1403" t="inlineStr"/>
+      <c r="B1403" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1403" t="inlineStr">
         <is>
           <t>POLPA-202509-4604</t>
@@ -34423,7 +34589,9 @@
       </c>
     </row>
     <row r="1424">
-      <c r="A1424" t="inlineStr"/>
+      <c r="A1424" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1424" t="n">
         <v>107.3</v>
       </c>
@@ -34520,7 +34688,9 @@
       <c r="A1428" t="n">
         <v>166.59</v>
       </c>
-      <c r="B1428" t="inlineStr"/>
+      <c r="B1428" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1428" t="inlineStr">
         <is>
           <t>POLPA-202509-4568</t>
@@ -34614,7 +34784,9 @@
       <c r="A1432" t="n">
         <v>601.3</v>
       </c>
-      <c r="B1432" t="inlineStr"/>
+      <c r="B1432" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1432" t="inlineStr">
         <is>
           <t>POLPA-202509-9458</t>
@@ -35377,7 +35549,9 @@
       </c>
     </row>
     <row r="1464">
-      <c r="A1464" t="inlineStr"/>
+      <c r="A1464" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1464" t="n">
         <v>39.64</v>
       </c>
@@ -35722,7 +35896,9 @@
           <t>POLPA-202509-2209</t>
         </is>
       </c>
-      <c r="D1478" t="inlineStr"/>
+      <c r="D1478" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1478" t="n">
         <v>2.43</v>
       </c>
@@ -35744,7 +35920,9 @@
           <t>POLPA-202509-6576</t>
         </is>
       </c>
-      <c r="D1479" t="inlineStr"/>
+      <c r="D1479" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1479" t="n">
         <v>1.87</v>
       </c>
@@ -35827,7 +36005,9 @@
       </c>
     </row>
     <row r="1483">
-      <c r="A1483" t="inlineStr"/>
+      <c r="A1483" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1483" t="n">
         <v>66.29000000000001</v>
       </c>
@@ -36460,7 +36640,9 @@
           <t>POLPA-202509-6958</t>
         </is>
       </c>
-      <c r="D1509" t="inlineStr"/>
+      <c r="D1509" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1509" t="n">
         <v>1.18</v>
       </c>
@@ -36711,7 +36893,9 @@
       </c>
     </row>
     <row r="1520">
-      <c r="A1520" t="inlineStr"/>
+      <c r="A1520" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1520" t="n">
         <v>369.28</v>
       </c>
@@ -36792,7 +36976,9 @@
           <t>POLPA-202509-2042</t>
         </is>
       </c>
-      <c r="D1523" t="inlineStr"/>
+      <c r="D1523" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1523" t="n">
         <v>2.64</v>
       </c>
@@ -36950,7 +37136,9 @@
       <c r="A1530" t="n">
         <v>1087.48</v>
       </c>
-      <c r="B1530" t="inlineStr"/>
+      <c r="B1530" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1530" t="inlineStr">
         <is>
           <t>POLPA-202509-2711</t>
@@ -37428,7 +37616,9 @@
       <c r="A1550" t="n">
         <v>1383.74</v>
       </c>
-      <c r="B1550" t="inlineStr"/>
+      <c r="B1550" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1550" t="inlineStr">
         <is>
           <t>POLPA-202509-8042</t>
@@ -37615,7 +37805,9 @@
       </c>
     </row>
     <row r="1558">
-      <c r="A1558" t="inlineStr"/>
+      <c r="A1558" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1558" t="n">
         <v>275.19</v>
       </c>
@@ -37808,7 +38000,9 @@
       <c r="A1566" t="n">
         <v>268.18</v>
       </c>
-      <c r="B1566" t="inlineStr"/>
+      <c r="B1566" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1566" t="inlineStr">
         <is>
           <t>POLPA-202509-8323</t>
@@ -37830,7 +38024,9 @@
       <c r="A1567" t="n">
         <v>147.62</v>
       </c>
-      <c r="B1567" t="inlineStr"/>
+      <c r="B1567" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1567" t="inlineStr">
         <is>
           <t>POLPA-202509-5220</t>
@@ -38233,7 +38429,9 @@
       </c>
     </row>
     <row r="1584">
-      <c r="A1584" t="inlineStr"/>
+      <c r="A1584" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1584" t="n">
         <v>407.97</v>
       </c>
@@ -38594,7 +38792,9 @@
       <c r="A1599" t="n">
         <v>553.49</v>
       </c>
-      <c r="B1599" t="inlineStr"/>
+      <c r="B1599" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1599" t="inlineStr">
         <is>
           <t>POLPA-202509-2227</t>
@@ -38856,7 +39056,9 @@
       <c r="A1610" t="n">
         <v>316.37</v>
       </c>
-      <c r="B1610" t="inlineStr"/>
+      <c r="B1610" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1610" t="inlineStr">
         <is>
           <t>POLPA-202509-5499</t>
@@ -39547,8 +39749,12 @@
       </c>
     </row>
     <row r="1639">
-      <c r="A1639" t="inlineStr"/>
-      <c r="B1639" t="inlineStr"/>
+      <c r="A1639" t="n">
+        <v>578.7460611353711</v>
+      </c>
+      <c r="B1639" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1639" t="inlineStr">
         <is>
           <t>POLPA-202509-2450</t>
@@ -39698,7 +39904,9 @@
           <t>POLPA-202509-5404</t>
         </is>
       </c>
-      <c r="D1645" t="inlineStr"/>
+      <c r="D1645" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1645" t="n">
         <v>1.48</v>
       </c>
@@ -40776,7 +40984,9 @@
           <t>POLPA-202509-7600</t>
         </is>
       </c>
-      <c r="D1690" t="inlineStr"/>
+      <c r="D1690" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1690" t="n">
         <v>2.4</v>
       </c>
@@ -41459,7 +41669,9 @@
       </c>
     </row>
     <row r="1719">
-      <c r="A1719" t="inlineStr"/>
+      <c r="A1719" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1719" t="n">
         <v>321.27</v>
       </c>
@@ -42348,7 +42560,9 @@
       <c r="A1756" t="n">
         <v>1490.98</v>
       </c>
-      <c r="B1756" t="inlineStr"/>
+      <c r="B1756" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1756" t="inlineStr">
         <is>
           <t>POLPA-202509-1329</t>
@@ -42706,13 +42920,17 @@
       <c r="A1771" t="n">
         <v>114.05</v>
       </c>
-      <c r="B1771" t="inlineStr"/>
+      <c r="B1771" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1771" t="inlineStr">
         <is>
           <t>POLPA-202509-2832</t>
         </is>
       </c>
-      <c r="D1771" t="inlineStr"/>
+      <c r="D1771" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1771" t="n">
         <v>2.7</v>
       </c>
@@ -43094,7 +43312,9 @@
           <t>POLPA-202509-8583</t>
         </is>
       </c>
-      <c r="D1787" t="inlineStr"/>
+      <c r="D1787" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1787" t="n">
         <v>2.28</v>
       </c>
@@ -43441,7 +43661,9 @@
       </c>
     </row>
     <row r="1802">
-      <c r="A1802" t="inlineStr"/>
+      <c r="A1802" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1802" t="n">
         <v>22.77</v>
       </c>
@@ -43706,7 +43928,9 @@
       <c r="A1813" t="n">
         <v>420.57</v>
       </c>
-      <c r="B1813" t="inlineStr"/>
+      <c r="B1813" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1813" t="inlineStr">
         <is>
           <t>POLPA-202509-8835</t>
@@ -43736,7 +43960,9 @@
           <t>POLPA-202509-8532</t>
         </is>
       </c>
-      <c r="D1814" t="inlineStr"/>
+      <c r="D1814" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1814" t="n">
         <v>1.67</v>
       </c>
@@ -43750,7 +43976,9 @@
       <c r="A1815" t="n">
         <v>315.4</v>
       </c>
-      <c r="B1815" t="inlineStr"/>
+      <c r="B1815" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1815" t="inlineStr">
         <is>
           <t>POLPA-202509-1969</t>
@@ -43852,7 +44080,9 @@
           <t>POLPA-202509-8294</t>
         </is>
       </c>
-      <c r="D1819" t="inlineStr"/>
+      <c r="D1819" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1819" t="n">
         <v>3.04</v>
       </c>
@@ -43970,7 +44200,9 @@
           <t>POLPA-202509-6883</t>
         </is>
       </c>
-      <c r="D1824" t="inlineStr"/>
+      <c r="D1824" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1824" t="n">
         <v>1.64</v>
       </c>
@@ -44365,7 +44597,9 @@
       </c>
     </row>
     <row r="1841">
-      <c r="A1841" t="inlineStr"/>
+      <c r="A1841" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1841" t="n">
         <v>156.14</v>
       </c>
@@ -44390,7 +44624,9 @@
       <c r="A1842" t="n">
         <v>197.74</v>
       </c>
-      <c r="B1842" t="inlineStr"/>
+      <c r="B1842" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1842" t="inlineStr">
         <is>
           <t>POLPA-202509-7752</t>
@@ -44556,7 +44792,9 @@
       <c r="A1849" t="n">
         <v>109.53</v>
       </c>
-      <c r="B1849" t="inlineStr"/>
+      <c r="B1849" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1849" t="inlineStr">
         <is>
           <t>POLPA-202509-4339</t>
@@ -44647,7 +44885,9 @@
       </c>
     </row>
     <row r="1853">
-      <c r="A1853" t="inlineStr"/>
+      <c r="A1853" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1853" t="n">
         <v>62.82</v>
       </c>
@@ -44669,7 +44909,9 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" t="inlineStr"/>
+      <c r="A1854" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1854" t="n">
         <v>268.19</v>
       </c>
@@ -44883,7 +45125,9 @@
       </c>
     </row>
     <row r="1863">
-      <c r="A1863" t="inlineStr"/>
+      <c r="A1863" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1863" t="n">
         <v>452.97</v>
       </c>
@@ -45316,7 +45560,9 @@
       <c r="A1881" t="n">
         <v>410.82</v>
       </c>
-      <c r="B1881" t="inlineStr"/>
+      <c r="B1881" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1881" t="inlineStr">
         <is>
           <t>POLPA-202509-2156</t>
@@ -45647,7 +45893,9 @@
       </c>
     </row>
     <row r="1895">
-      <c r="A1895" t="inlineStr"/>
+      <c r="A1895" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B1895" t="n">
         <v>308.9</v>
       </c>
@@ -45776,7 +46024,9 @@
           <t>POLPA-202509-5321</t>
         </is>
       </c>
-      <c r="D1900" t="inlineStr"/>
+      <c r="D1900" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1900" t="n">
         <v>1.62</v>
       </c>
@@ -45798,7 +46048,9 @@
           <t>POLPA-202509-8334</t>
         </is>
       </c>
-      <c r="D1901" t="inlineStr"/>
+      <c r="D1901" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1901" t="n">
         <v>0.77</v>
       </c>
@@ -46756,7 +47008,9 @@
           <t>POLPA-202510-7906</t>
         </is>
       </c>
-      <c r="D1941" t="inlineStr"/>
+      <c r="D1941" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1941" t="n">
         <v>2.87</v>
       </c>
@@ -46818,7 +47072,9 @@
       <c r="A1944" t="n">
         <v>305.34</v>
       </c>
-      <c r="B1944" t="inlineStr"/>
+      <c r="B1944" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C1944" t="inlineStr">
         <is>
           <t>POLPA-202510-4782</t>
@@ -47688,7 +47944,9 @@
           <t>POLPA-202510-2962</t>
         </is>
       </c>
-      <c r="D1980" t="inlineStr"/>
+      <c r="D1980" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E1980" t="n">
         <v>2.46</v>
       </c>
@@ -48286,7 +48544,9 @@
           <t>POLPA-202510-7219</t>
         </is>
       </c>
-      <c r="D2005" t="inlineStr"/>
+      <c r="D2005" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2005" t="n">
         <v>0.3</v>
       </c>
@@ -50388,7 +50648,9 @@
       <c r="A2093" t="n">
         <v>1914.44</v>
       </c>
-      <c r="B2093" t="inlineStr"/>
+      <c r="B2093" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2093" t="inlineStr">
         <is>
           <t>POLPA-202510-1512</t>
@@ -50418,7 +50680,9 @@
           <t>POLPA-202510-4858</t>
         </is>
       </c>
-      <c r="D2094" t="inlineStr"/>
+      <c r="D2094" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2094" t="n">
         <v>2.39</v>
       </c>
@@ -50824,7 +51088,9 @@
           <t>POLPA-202510-3757</t>
         </is>
       </c>
-      <c r="D2111" t="inlineStr"/>
+      <c r="D2111" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2111" t="n">
         <v>1.66</v>
       </c>
@@ -50982,7 +51248,9 @@
       <c r="A2118" t="n">
         <v>446.92</v>
       </c>
-      <c r="B2118" t="inlineStr"/>
+      <c r="B2118" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2118" t="inlineStr">
         <is>
           <t>POLPA-202510-9096</t>
@@ -51252,7 +51520,9 @@
           <t>POLPA-202510-7881</t>
         </is>
       </c>
-      <c r="D2129" t="inlineStr"/>
+      <c r="D2129" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2129" t="n">
         <v>0.62</v>
       </c>
@@ -51418,7 +51688,9 @@
           <t>POLPA-202510-9978</t>
         </is>
       </c>
-      <c r="D2136" t="inlineStr"/>
+      <c r="D2136" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2136" t="n">
         <v>2.19</v>
       </c>
@@ -51632,7 +51904,9 @@
           <t>POLPA-202510-8405</t>
         </is>
       </c>
-      <c r="D2145" t="inlineStr"/>
+      <c r="D2145" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2145" t="n">
         <v>2.6</v>
       </c>
@@ -51750,7 +52024,9 @@
           <t>POLPA-202510-6980</t>
         </is>
       </c>
-      <c r="D2150" t="inlineStr"/>
+      <c r="D2150" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2150" t="n">
         <v>1.84</v>
       </c>
@@ -52025,7 +52301,9 @@
       </c>
     </row>
     <row r="2162">
-      <c r="A2162" t="inlineStr"/>
+      <c r="A2162" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2162" t="n">
         <v>725.5</v>
       </c>
@@ -52098,7 +52376,9 @@
       <c r="A2165" t="n">
         <v>272.31</v>
       </c>
-      <c r="B2165" t="inlineStr"/>
+      <c r="B2165" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2165" t="inlineStr">
         <is>
           <t>POLPA-202510-3746</t>
@@ -53136,7 +53416,9 @@
           <t>POLPA-202510-4845</t>
         </is>
       </c>
-      <c r="D2208" t="inlineStr"/>
+      <c r="D2208" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2208" t="n">
         <v>1.02</v>
       </c>
@@ -53507,7 +53789,9 @@
       </c>
     </row>
     <row r="2224">
-      <c r="A2224" t="inlineStr"/>
+      <c r="A2224" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2224" t="n">
         <v>236.59</v>
       </c>
@@ -54092,7 +54376,9 @@
           <t>POLPA-202510-7274</t>
         </is>
       </c>
-      <c r="D2248" t="inlineStr"/>
+      <c r="D2248" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2248" t="n">
         <v>3.51</v>
       </c>
@@ -54658,7 +54944,9 @@
       <c r="A2272" t="n">
         <v>326.21</v>
       </c>
-      <c r="B2272" t="inlineStr"/>
+      <c r="B2272" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2272" t="inlineStr">
         <is>
           <t>POLPA-202510-9622</t>
@@ -55040,7 +55328,9 @@
       <c r="A2288" t="n">
         <v>92.97</v>
       </c>
-      <c r="B2288" t="inlineStr"/>
+      <c r="B2288" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2288" t="inlineStr">
         <is>
           <t>POLPA-202510-6246</t>
@@ -55590,7 +55880,9 @@
       <c r="A2311" t="n">
         <v>449.03</v>
       </c>
-      <c r="B2311" t="inlineStr"/>
+      <c r="B2311" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2311" t="inlineStr">
         <is>
           <t>POLPA-202510-5566</t>
@@ -55921,7 +56213,9 @@
       </c>
     </row>
     <row r="2325">
-      <c r="A2325" t="inlineStr"/>
+      <c r="A2325" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2325" t="n">
         <v>225.15</v>
       </c>
@@ -56170,7 +56464,9 @@
           <t>POLPA-202510-1628</t>
         </is>
       </c>
-      <c r="D2335" t="inlineStr"/>
+      <c r="D2335" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2335" t="n">
         <v>1.11</v>
       </c>
@@ -56312,7 +56608,9 @@
           <t>POLPA-202510-1868</t>
         </is>
       </c>
-      <c r="D2341" t="inlineStr"/>
+      <c r="D2341" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2341" t="n">
         <v>0.48</v>
       </c>
@@ -56526,7 +56824,9 @@
           <t>POLPA-202510-6062</t>
         </is>
       </c>
-      <c r="D2350" t="inlineStr"/>
+      <c r="D2350" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2350" t="n">
         <v>2.59</v>
       </c>
@@ -56756,7 +57056,9 @@
       <c r="A2360" t="n">
         <v>186.77</v>
       </c>
-      <c r="B2360" t="inlineStr"/>
+      <c r="B2360" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2360" t="inlineStr">
         <is>
           <t>POLPA-202510-8090</t>
@@ -57626,7 +57928,9 @@
           <t>POLPA-202510-1547</t>
         </is>
       </c>
-      <c r="D2396" t="inlineStr"/>
+      <c r="D2396" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2396" t="n">
         <v>2.29</v>
       </c>
@@ -58120,7 +58424,9 @@
       <c r="A2417" t="n">
         <v>146.37</v>
       </c>
-      <c r="B2417" t="inlineStr"/>
+      <c r="B2417" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2417" t="inlineStr">
         <is>
           <t>POLPA-202510-5838</t>
@@ -58331,7 +58637,9 @@
       </c>
     </row>
     <row r="2426">
-      <c r="A2426" t="inlineStr"/>
+      <c r="A2426" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2426" t="n">
         <v>142.11</v>
       </c>
@@ -58353,7 +58661,9 @@
       </c>
     </row>
     <row r="2427">
-      <c r="A2427" t="inlineStr"/>
+      <c r="A2427" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2427" t="n">
         <v>728.98</v>
       </c>
@@ -59674,7 +59984,9 @@
       <c r="A2482" t="n">
         <v>272.79</v>
       </c>
-      <c r="B2482" t="inlineStr"/>
+      <c r="B2482" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2482" t="inlineStr">
         <is>
           <t>POLPA-202510-7486</t>
@@ -59885,7 +60197,9 @@
       </c>
     </row>
     <row r="2491">
-      <c r="A2491" t="inlineStr"/>
+      <c r="A2491" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2491" t="n">
         <v>120.71</v>
       </c>
@@ -60075,7 +60389,9 @@
       </c>
     </row>
     <row r="2499">
-      <c r="A2499" t="inlineStr"/>
+      <c r="A2499" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2499" t="n">
         <v>5.37</v>
       </c>
@@ -60972,7 +61288,9 @@
           <t>POLPA-202510-8906</t>
         </is>
       </c>
-      <c r="D2536" t="inlineStr"/>
+      <c r="D2536" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2536" t="n">
         <v>1.69</v>
       </c>
@@ -61130,7 +61448,9 @@
       <c r="A2543" t="n">
         <v>594</v>
       </c>
-      <c r="B2543" t="inlineStr"/>
+      <c r="B2543" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2543" t="inlineStr">
         <is>
           <t>POLPA-202510-3310</t>
@@ -61176,7 +61496,9 @@
       <c r="A2545" t="n">
         <v>832.9299999999999</v>
       </c>
-      <c r="B2545" t="inlineStr"/>
+      <c r="B2545" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2545" t="inlineStr">
         <is>
           <t>POLPA-202510-4616</t>
@@ -61675,7 +61997,9 @@
       </c>
     </row>
     <row r="2566">
-      <c r="A2566" t="inlineStr"/>
+      <c r="A2566" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2566" t="n">
         <v>138.52</v>
       </c>
@@ -61748,7 +62072,9 @@
       <c r="A2569" t="n">
         <v>433.6</v>
       </c>
-      <c r="B2569" t="inlineStr"/>
+      <c r="B2569" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2569" t="inlineStr">
         <is>
           <t>POLPA-202510-4391</t>
@@ -62642,7 +62968,9 @@
           <t>POLPA-202510-6314</t>
         </is>
       </c>
-      <c r="D2606" t="inlineStr"/>
+      <c r="D2606" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2606" t="n">
         <v>0.3</v>
       </c>
@@ -62800,7 +63128,9 @@
       <c r="A2613" t="n">
         <v>462.35</v>
       </c>
-      <c r="B2613" t="inlineStr"/>
+      <c r="B2613" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2613" t="inlineStr">
         <is>
           <t>POLPA-202510-3864</t>
@@ -62854,7 +63184,9 @@
           <t>POLPA-202510-7096</t>
         </is>
       </c>
-      <c r="D2615" t="inlineStr"/>
+      <c r="D2615" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2615" t="n">
         <v>2.63</v>
       </c>
@@ -63396,7 +63728,9 @@
       <c r="A2638" t="n">
         <v>279.58</v>
       </c>
-      <c r="B2638" t="inlineStr"/>
+      <c r="B2638" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2638" t="inlineStr">
         <is>
           <t>POLPA-202511-6057</t>
@@ -64231,7 +64565,9 @@
       </c>
     </row>
     <row r="2673">
-      <c r="A2673" t="inlineStr"/>
+      <c r="A2673" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2673" t="n">
         <v>291.67</v>
       </c>
@@ -64264,7 +64600,9 @@
           <t>POLPA-202511-8538</t>
         </is>
       </c>
-      <c r="D2674" t="inlineStr"/>
+      <c r="D2674" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2674" t="n">
         <v>2.29</v>
       </c>
@@ -64646,7 +64984,9 @@
           <t>POLPA-202511-4167</t>
         </is>
       </c>
-      <c r="D2690" t="inlineStr"/>
+      <c r="D2690" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2690" t="n">
         <v>0.3</v>
       </c>
@@ -64836,7 +65176,9 @@
           <t>POLPA-202511-6638</t>
         </is>
       </c>
-      <c r="D2698" t="inlineStr"/>
+      <c r="D2698" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2698" t="n">
         <v>2.31</v>
       </c>
@@ -64858,7 +65200,9 @@
           <t>POLPA-202511-8625</t>
         </is>
       </c>
-      <c r="D2699" t="inlineStr"/>
+      <c r="D2699" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2699" t="n">
         <v>1.36</v>
       </c>
@@ -65544,7 +65888,9 @@
       <c r="A2728" t="n">
         <v>556.54</v>
       </c>
-      <c r="B2728" t="inlineStr"/>
+      <c r="B2728" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2728" t="inlineStr">
         <is>
           <t>POLPA-202511-1129</t>
@@ -65899,7 +66245,9 @@
       </c>
     </row>
     <row r="2743">
-      <c r="A2743" t="inlineStr"/>
+      <c r="A2743" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2743" t="n">
         <v>9.51</v>
       </c>
@@ -66316,7 +66664,9 @@
           <t>POLPA-202511-1965</t>
         </is>
       </c>
-      <c r="D2760" t="inlineStr"/>
+      <c r="D2760" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2760" t="n">
         <v>3.11</v>
       </c>
@@ -66842,7 +67192,9 @@
           <t>POLPA-202511-2822</t>
         </is>
       </c>
-      <c r="D2782" t="inlineStr"/>
+      <c r="D2782" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2782" t="n">
         <v>2.54</v>
       </c>
@@ -66864,7 +67216,9 @@
           <t>POLPA-202511-2319</t>
         </is>
       </c>
-      <c r="D2783" t="inlineStr"/>
+      <c r="D2783" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2783" t="n">
         <v>1.29</v>
       </c>
@@ -67558,7 +67912,9 @@
           <t>POLPA-202511-8167</t>
         </is>
       </c>
-      <c r="D2812" t="inlineStr"/>
+      <c r="D2812" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2812" t="n">
         <v>1.59</v>
       </c>
@@ -67572,7 +67928,9 @@
       <c r="A2813" t="n">
         <v>1857.5</v>
       </c>
-      <c r="B2813" t="inlineStr"/>
+      <c r="B2813" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2813" t="inlineStr">
         <is>
           <t>POLPA-202511-7064</t>
@@ -68130,7 +68488,9 @@
           <t>POLPA-202511-6824</t>
         </is>
       </c>
-      <c r="D2836" t="inlineStr"/>
+      <c r="D2836" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2836" t="n">
         <v>0.75</v>
       </c>
@@ -69328,7 +69688,9 @@
           <t>POLPA-202511-5149</t>
         </is>
       </c>
-      <c r="D2886" t="inlineStr"/>
+      <c r="D2886" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2886" t="n">
         <v>0.54</v>
       </c>
@@ -69867,7 +70229,9 @@
       </c>
     </row>
     <row r="2909">
-      <c r="A2909" t="inlineStr"/>
+      <c r="A2909" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2909" t="n">
         <v>670.12</v>
       </c>
@@ -69937,7 +70301,9 @@
       </c>
     </row>
     <row r="2912">
-      <c r="A2912" t="inlineStr"/>
+      <c r="A2912" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2912" t="n">
         <v>41.95</v>
       </c>
@@ -70162,7 +70528,9 @@
           <t>POLPA-202511-6205</t>
         </is>
       </c>
-      <c r="D2921" t="inlineStr"/>
+      <c r="D2921" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2921" t="n">
         <v>2.51</v>
       </c>
@@ -70677,7 +71045,9 @@
       </c>
     </row>
     <row r="2943">
-      <c r="A2943" t="inlineStr"/>
+      <c r="A2943" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B2943" t="n">
         <v>440.78</v>
       </c>
@@ -71086,7 +71456,9 @@
       <c r="A2960" t="n">
         <v>632.34</v>
       </c>
-      <c r="B2960" t="inlineStr"/>
+      <c r="B2960" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2960" t="inlineStr">
         <is>
           <t>POLPA-202511-9152</t>
@@ -71420,7 +71792,9 @@
       <c r="A2974" t="n">
         <v>652.37</v>
       </c>
-      <c r="B2974" t="inlineStr"/>
+      <c r="B2974" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C2974" t="inlineStr">
         <is>
           <t>POLPA-202511-6501</t>
@@ -71834,7 +72208,9 @@
           <t>POLPA-202511-1562</t>
         </is>
       </c>
-      <c r="D2991" t="inlineStr"/>
+      <c r="D2991" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E2991" t="n">
         <v>2.83</v>
       </c>
@@ -72277,7 +72653,9 @@
       </c>
     </row>
     <row r="3010">
-      <c r="A3010" t="inlineStr"/>
+      <c r="A3010" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3010" t="n">
         <v>369.34</v>
       </c>
@@ -72454,7 +72832,9 @@
           <t>POLPA-202511-1860</t>
         </is>
       </c>
-      <c r="D3017" t="inlineStr"/>
+      <c r="D3017" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3017" t="n">
         <v>1.17</v>
       </c>
@@ -72492,7 +72872,9 @@
       <c r="A3019" t="n">
         <v>90.67</v>
       </c>
-      <c r="B3019" t="inlineStr"/>
+      <c r="B3019" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3019" t="inlineStr">
         <is>
           <t>POLPA-202511-1329</t>
@@ -73495,7 +73877,9 @@
       </c>
     </row>
     <row r="3061">
-      <c r="A3061" t="inlineStr"/>
+      <c r="A3061" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3061" t="n">
         <v>502.71</v>
       </c>
@@ -74096,7 +74480,9 @@
       <c r="A3086" t="n">
         <v>125.64</v>
       </c>
-      <c r="B3086" t="inlineStr"/>
+      <c r="B3086" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3086" t="inlineStr">
         <is>
           <t>POLPA-202511-4782</t>
@@ -74670,7 +75056,9 @@
       <c r="A3110" t="n">
         <v>251.25</v>
       </c>
-      <c r="B3110" t="inlineStr"/>
+      <c r="B3110" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3110" t="inlineStr">
         <is>
           <t>POLPA-202511-7276</t>
@@ -75252,7 +75640,9 @@
           <t>POLPA-202511-4602</t>
         </is>
       </c>
-      <c r="D3134" t="inlineStr"/>
+      <c r="D3134" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3134" t="n">
         <v>1.74</v>
       </c>
@@ -75263,7 +75653,9 @@
       </c>
     </row>
     <row r="3135">
-      <c r="A3135" t="inlineStr"/>
+      <c r="A3135" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3135" t="n">
         <v>120.7</v>
       </c>
@@ -75504,7 +75896,9 @@
       <c r="A3145" t="n">
         <v>84.7</v>
       </c>
-      <c r="B3145" t="inlineStr"/>
+      <c r="B3145" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3145" t="inlineStr">
         <is>
           <t>POLPA-202511-3208</t>
@@ -75990,7 +76384,9 @@
           <t>POLPA-202512-8075</t>
         </is>
       </c>
-      <c r="D3165" t="inlineStr"/>
+      <c r="D3165" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3165" t="n">
         <v>1.62</v>
       </c>
@@ -76132,7 +76528,9 @@
           <t>POLPA-202512-6721</t>
         </is>
       </c>
-      <c r="D3171" t="inlineStr"/>
+      <c r="D3171" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3171" t="n">
         <v>1.81</v>
       </c>
@@ -76215,7 +76613,9 @@
       </c>
     </row>
     <row r="3175">
-      <c r="A3175" t="inlineStr"/>
+      <c r="A3175" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3175" t="n">
         <v>96.2</v>
       </c>
@@ -77440,7 +77840,9 @@
       <c r="A3226" t="n">
         <v>126.35</v>
       </c>
-      <c r="B3226" t="inlineStr"/>
+      <c r="B3226" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3226" t="inlineStr">
         <is>
           <t>POLPA-202512-4623</t>
@@ -77534,13 +77936,17 @@
       <c r="A3230" t="n">
         <v>194.91</v>
       </c>
-      <c r="B3230" t="inlineStr"/>
+      <c r="B3230" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3230" t="inlineStr">
         <is>
           <t>POLPA-202512-9292</t>
         </is>
       </c>
-      <c r="D3230" t="inlineStr"/>
+      <c r="D3230" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3230" t="n">
         <v>2.03</v>
       </c>
@@ -77650,7 +78056,9 @@
       <c r="A3235" t="n">
         <v>199.7</v>
       </c>
-      <c r="B3235" t="inlineStr"/>
+      <c r="B3235" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3235" t="inlineStr">
         <is>
           <t>POLPA-202512-5613</t>
@@ -77984,7 +78392,9 @@
       <c r="A3249" t="n">
         <v>138.37</v>
       </c>
-      <c r="B3249" t="inlineStr"/>
+      <c r="B3249" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3249" t="inlineStr">
         <is>
           <t>POLPA-202512-1958</t>
@@ -78126,7 +78536,9 @@
       <c r="A3255" t="n">
         <v>107.19</v>
       </c>
-      <c r="B3255" t="inlineStr"/>
+      <c r="B3255" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3255" t="inlineStr">
         <is>
           <t>POLPA-202512-6878</t>
@@ -78865,7 +79277,9 @@
       </c>
     </row>
     <row r="3286">
-      <c r="A3286" t="inlineStr"/>
+      <c r="A3286" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3286" t="n">
         <v>35.58</v>
       </c>
@@ -78914,7 +79328,9 @@
       <c r="A3288" t="n">
         <v>949.4</v>
       </c>
-      <c r="B3288" t="inlineStr"/>
+      <c r="B3288" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3288" t="inlineStr">
         <is>
           <t>POLPA-202512-4021</t>
@@ -79341,7 +79757,9 @@
       </c>
     </row>
     <row r="3306">
-      <c r="A3306" t="inlineStr"/>
+      <c r="A3306" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3306" t="n">
         <v>8.44</v>
       </c>
@@ -79822,13 +80240,17 @@
       <c r="A3326" t="n">
         <v>433.74</v>
       </c>
-      <c r="B3326" t="inlineStr"/>
+      <c r="B3326" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3326" t="inlineStr">
         <is>
           <t>POLPA-202512-7572</t>
         </is>
       </c>
-      <c r="D3326" t="inlineStr"/>
+      <c r="D3326" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3326" t="n">
         <v>1.41</v>
       </c>
@@ -79970,7 +80392,9 @@
           <t>POLPA-202512-6370</t>
         </is>
       </c>
-      <c r="D3332" t="inlineStr"/>
+      <c r="D3332" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3332" t="n">
         <v>3.61</v>
       </c>
@@ -80224,7 +80648,9 @@
       <c r="A3343" t="n">
         <v>204.5</v>
       </c>
-      <c r="B3343" t="inlineStr"/>
+      <c r="B3343" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3343" t="inlineStr">
         <is>
           <t>POLPA-202512-4934</t>
@@ -80566,7 +80992,9 @@
           <t>POLPA-202512-5570</t>
         </is>
       </c>
-      <c r="D3357" t="inlineStr"/>
+      <c r="D3357" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3357" t="n">
         <v>0.45</v>
       </c>
@@ -81044,7 +81472,9 @@
           <t>POLPA-202512-4425</t>
         </is>
       </c>
-      <c r="D3377" t="inlineStr"/>
+      <c r="D3377" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3377" t="n">
         <v>2.28</v>
       </c>
@@ -81538,7 +81968,9 @@
       <c r="A3398" t="n">
         <v>380.8</v>
       </c>
-      <c r="B3398" t="inlineStr"/>
+      <c r="B3398" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3398" t="inlineStr">
         <is>
           <t>POLPA-202512-3501</t>
@@ -81736,7 +82168,9 @@
           <t>POLPA-202512-5003</t>
         </is>
       </c>
-      <c r="D3406" t="inlineStr"/>
+      <c r="D3406" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3406" t="n">
         <v>1.46</v>
       </c>
@@ -81990,7 +82424,9 @@
       <c r="A3417" t="n">
         <v>517.16</v>
       </c>
-      <c r="B3417" t="inlineStr"/>
+      <c r="B3417" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3417" t="inlineStr">
         <is>
           <t>POLPA-202512-1598</t>
@@ -82441,7 +82877,9 @@
       </c>
     </row>
     <row r="3436">
-      <c r="A3436" t="inlineStr"/>
+      <c r="A3436" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3436" t="n">
         <v>24.15</v>
       </c>
@@ -82487,7 +82925,9 @@
       </c>
     </row>
     <row r="3438">
-      <c r="A3438" t="inlineStr"/>
+      <c r="A3438" t="n">
+        <v>578.7460611353711</v>
+      </c>
       <c r="B3438" t="n">
         <v>31.02</v>
       </c>
@@ -82512,7 +82952,9 @@
       <c r="A3439" t="n">
         <v>387.15</v>
       </c>
-      <c r="B3439" t="inlineStr"/>
+      <c r="B3439" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3439" t="inlineStr">
         <is>
           <t>POLPA-202512-2738</t>
@@ -82902,7 +83344,9 @@
           <t>POLPA-202512-1167</t>
         </is>
       </c>
-      <c r="D3455" t="inlineStr"/>
+      <c r="D3455" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3455" t="n">
         <v>1.66</v>
       </c>
@@ -83276,7 +83720,9 @@
       <c r="A3471" t="n">
         <v>486.76</v>
       </c>
-      <c r="B3471" t="inlineStr"/>
+      <c r="B3471" t="n">
+        <v>196.3473868613139</v>
+      </c>
       <c r="C3471" t="inlineStr">
         <is>
           <t>POLPA-202512-3980</t>
@@ -83954,7 +84400,9 @@
           <t>POLPA-202512-6496</t>
         </is>
       </c>
-      <c r="D3499" t="inlineStr"/>
+      <c r="D3499" t="n">
+        <v>8.387342513917375</v>
+      </c>
       <c r="E3499" t="n">
         <v>2.84</v>
       </c>
